--- a/docs/validation/validation-tracker.xlsx
+++ b/docs/validation/validation-tracker.xlsx
@@ -133,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ValidationItems" displayName="ValidationItems" ref="A1:S196" totalsRowShown="0">
-  <autoFilter ref="A1:S196"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ValidationItems" displayName="ValidationItems" ref="A1:S211" totalsRowShown="0">
+  <autoFilter ref="A1:S211"/>
   <tableColumns count="19">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -267,39 +267,39 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6)</f>
         <v>9</v>
       </c>
       <c r="C6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,C$5)</f>
         <v>9</v>
       </c>
       <c r="D6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A6,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$G$2:$G$211,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K6" s="4">
@@ -318,40 +318,40 @@
         </is>
       </c>
       <c r="B7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7)</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7)</f>
+        <v>10</v>
       </c>
       <c r="C7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$F$2:$F$196,C$5)</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,C$5)</f>
+        <v>10</v>
       </c>
       <c r="D7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A7,Items!$G$2:$G$196,"Pending")</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$G$2:$G$211,"Pending")</f>
+        <v>10</v>
       </c>
       <c r="K7" s="4">
         <f>IF(B7-G7=0,0,(D7+E7+F7)/(B7-G7))</f>
@@ -369,39 +369,39 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8)</f>
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,C$5)</f>
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,F$5)</f>
         <v>1</v>
       </c>
       <c r="G8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A8,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$G$2:$G$211,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K8" s="4">
@@ -420,39 +420,39 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9)</f>
         <v>9</v>
       </c>
       <c r="C9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,C$5)</f>
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A9,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$G$2:$G$211,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K9" s="4">
@@ -471,39 +471,39 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10)</f>
         <v>9</v>
       </c>
       <c r="C10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,C$5)</f>
         <v>9</v>
       </c>
       <c r="D10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A10,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$G$2:$G$211,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K10" s="4">
@@ -522,39 +522,39 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11)</f>
         <v>5</v>
       </c>
       <c r="C11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,C$5)</f>
         <v>5</v>
       </c>
       <c r="D11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A11,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$G$2:$G$211,"Pending")</f>
         <v>5</v>
       </c>
       <c r="K11" s="4">
@@ -573,39 +573,39 @@
         </is>
       </c>
       <c r="B12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,C$5)</f>
         <v>5</v>
       </c>
       <c r="D12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A12,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$G$2:$G$211,"Pending")</f>
         <v>5</v>
       </c>
       <c r="K12" s="4">
@@ -624,39 +624,39 @@
         </is>
       </c>
       <c r="B13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13)</f>
         <v>9</v>
       </c>
       <c r="C13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,C$5)</f>
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A13,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$G$2:$G$211,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K13" s="4">
@@ -675,39 +675,39 @@
         </is>
       </c>
       <c r="B14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14)</f>
         <v>17</v>
       </c>
       <c r="C14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,C$5)</f>
         <v>17</v>
       </c>
       <c r="D14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A14,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$G$2:$G$211,"Pending")</f>
         <v>17</v>
       </c>
       <c r="K14" s="4">
@@ -726,39 +726,39 @@
         </is>
       </c>
       <c r="B15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,C$5)</f>
         <v>4</v>
       </c>
       <c r="D15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A15,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$G$2:$G$211,"Pending")</f>
         <v>4</v>
       </c>
       <c r="K15" s="4">
@@ -777,39 +777,39 @@
         </is>
       </c>
       <c r="B16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16)</f>
         <v>9</v>
       </c>
       <c r="C16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,C$5)</f>
         <v>9</v>
       </c>
       <c r="D16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A16,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$G$2:$G$211,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K16" s="4">
@@ -828,39 +828,39 @@
         </is>
       </c>
       <c r="B17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17)</f>
         <v>15</v>
       </c>
       <c r="C17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,C$5)</f>
         <v>14</v>
       </c>
       <c r="D17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,F$5)</f>
         <v>1</v>
       </c>
       <c r="G17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A17,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$G$2:$G$211,"Pending")</f>
         <v>15</v>
       </c>
       <c r="K17" s="4">
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18)</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18)</f>
+        <v>10</v>
       </c>
       <c r="C18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$F$2:$F$196,C$5)</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,C$5)</f>
+        <v>10</v>
       </c>
       <c r="D18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A18,Items!$G$2:$G$196,"Pending")</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$G$2:$G$211,"Pending")</f>
+        <v>10</v>
       </c>
       <c r="K18" s="4">
         <f>IF(B18-G18=0,0,(D18+E18+F18)/(B18-G18))</f>
@@ -930,40 +930,40 @@
         </is>
       </c>
       <c r="B19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19)</f>
-        <v>4</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19)</f>
+        <v>7</v>
       </c>
       <c r="C19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$F$2:$F$196,C$5)</f>
-        <v>4</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,C$5)</f>
+        <v>7</v>
       </c>
       <c r="D19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A19,Items!$G$2:$G$196,"Pending")</f>
-        <v>4</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$G$2:$G$211,"Pending")</f>
+        <v>7</v>
       </c>
       <c r="K19" s="4">
         <f>IF(B19-G19=0,0,(D19+E19+F19)/(B19-G19))</f>
@@ -981,40 +981,40 @@
         </is>
       </c>
       <c r="B20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20)</f>
-        <v>22</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20)</f>
+        <v>23</v>
       </c>
       <c r="C20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$F$2:$F$196,C$5)</f>
-        <v>22</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,C$5)</f>
+        <v>23</v>
       </c>
       <c r="D20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A20,Items!$G$2:$G$196,"Pending")</f>
-        <v>22</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$G$2:$G$211,"Pending")</f>
+        <v>23</v>
       </c>
       <c r="K20" s="4">
         <f>IF(B20-G20=0,0,(D20+E20+F20)/(B20-G20))</f>
@@ -1032,39 +1032,39 @@
         </is>
       </c>
       <c r="B21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,C$5)</f>
         <v>2</v>
       </c>
       <c r="D21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A21,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$G$2:$G$211,"Pending")</f>
         <v>2</v>
       </c>
       <c r="K21" s="4">
@@ -1083,39 +1083,39 @@
         </is>
       </c>
       <c r="B22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22)</f>
         <v>6</v>
       </c>
       <c r="C22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,C$5)</f>
         <v>6</v>
       </c>
       <c r="D22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A22,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$G$2:$G$211,"Pending")</f>
         <v>6</v>
       </c>
       <c r="K22" s="4">
@@ -1134,44 +1134,44 @@
         </is>
       </c>
       <c r="B23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23)</f>
+        <v>23</v>
+      </c>
+      <c r="C23" s="0">
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,C$5)</f>
         <v>22</v>
       </c>
-      <c r="C23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$F$2:$F$196,C$5)</f>
-        <v>21</v>
-      </c>
       <c r="D23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,F$5)</f>
         <v>1</v>
       </c>
       <c r="G23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A23,Items!$G$2:$G$196,"Pending")</f>
-        <v>22</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$G$2:$G$211,"Pending")</f>
+        <v>23</v>
       </c>
       <c r="K23" s="4">
         <f>IF(B23-G23=0,0,(D23+E23+F23)/(B23-G23))</f>
-        <v>0.045455</v>
+        <v>0.043478</v>
       </c>
       <c r="L23" s="4">
         <f>IF(B23-G23=0,0,H23/(B23-G23))</f>
@@ -1185,40 +1185,40 @@
         </is>
       </c>
       <c r="B24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24)</f>
-        <v>3</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24)</f>
+        <v>4</v>
       </c>
       <c r="C24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$F$2:$F$196,C$5)</f>
-        <v>1</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,C$5)</f>
+        <v>2</v>
       </c>
       <c r="D24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,G$5)</f>
         <v>2</v>
       </c>
       <c r="H24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A24,Items!$G$2:$G$196,"Pending")</f>
-        <v>3</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$G$2:$G$211,"Pending")</f>
+        <v>4</v>
       </c>
       <c r="K24" s="4">
         <f>IF(B24-G24=0,0,(D24+E24+F24)/(B24-G24))</f>
@@ -1236,40 +1236,40 @@
         </is>
       </c>
       <c r="B25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25)</f>
-        <v>3</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25)</f>
+        <v>8</v>
       </c>
       <c r="C25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$F$2:$F$196,C$5)</f>
-        <v>2</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,C$5)</f>
+        <v>7</v>
       </c>
       <c r="D25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,G$5)</f>
         <v>1</v>
       </c>
       <c r="H25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A25,Items!$G$2:$G$196,"Pending")</f>
-        <v>3</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$G$2:$G$211,"Pending")</f>
+        <v>8</v>
       </c>
       <c r="K25" s="4">
         <f>IF(B25-G25=0,0,(D25+E25+F25)/(B25-G25))</f>
@@ -1287,39 +1287,39 @@
         </is>
       </c>
       <c r="B26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26)</f>
         <v>3</v>
       </c>
       <c r="C26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$F$2:$F$196,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,C$5)</f>
         <v>3</v>
       </c>
       <c r="D26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A26,Items!$G$2:$G$196,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$G$2:$G$211,"Pending")</f>
         <v>3</v>
       </c>
       <c r="K26" s="4">
@@ -1338,40 +1338,40 @@
         </is>
       </c>
       <c r="B27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27)</f>
-        <v>12</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27)</f>
+        <v>14</v>
       </c>
       <c r="C27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$F$2:$F$196,C$5)</f>
-        <v>12</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,C$5)</f>
+        <v>14</v>
       </c>
       <c r="D27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$F$2:$F$196,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,D$5)</f>
         <v>0</v>
       </c>
       <c r="E27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$F$2:$F$196,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,E$5)</f>
         <v>0</v>
       </c>
       <c r="F27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$F$2:$F$196,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,F$5)</f>
         <v>0</v>
       </c>
       <c r="G27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$F$2:$F$196,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,G$5)</f>
         <v>0</v>
       </c>
       <c r="H27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$F$2:$F$196,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,H$5)</f>
         <v>0</v>
       </c>
       <c r="I27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$G$2:$G$196,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$G$2:$G$211,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$196,$A27,Items!$G$2:$G$196,"Pending")</f>
-        <v>12</v>
+        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$G$2:$G$211,"Pending")</f>
+        <v>14</v>
       </c>
       <c r="K27" s="4">
         <f>IF(B27-G27=0,0,(D27+E27+F27)/(B27-G27))</f>
@@ -1390,11 +1390,11 @@
       </c>
       <c r="B28" s="5">
         <f>SUM(B6:B27)</f>
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C28" s="5">
         <f>SUM(C6:C27)</f>
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="D28" s="5">
         <f>SUM(D6:D27)</f>
@@ -1422,11 +1422,11 @@
       </c>
       <c r="J28" s="5">
         <f>SUM(J6:J27)</f>
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="K28" s="4">
         <f>IF(B28-G28=0,0,(D28+E28+F28)/(B28-G28))</f>
-        <v>0.015385</v>
+        <v>0.014286</v>
       </c>
       <c r="L28" s="4">
         <f>IF(B28-G28=0,0,H28/(B28-G28))</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="B31" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$196,"Failed")</f>
+        <f>COUNTIFS(Items!$F$2:$F$211,"Failed")</f>
         <v>0</v>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B32" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$196,"Needs improvement")</f>
+        <f>COUNTIFS(Items!$F$2:$F$211,"Needs improvement")</f>
         <v>3</v>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B33" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$196,"Blocked")</f>
+        <f>COUNTIFS(Items!$F$2:$F$211,"Blocked")</f>
         <v>3</v>
       </c>
     </row>
@@ -1485,8 +1485,8 @@
         </is>
       </c>
       <c r="B34" s="0">
-        <f>COUNTIFS(Items!$L$2:$L$196,"&lt;&gt;",Items!$F$2:$F$196,"&lt;&gt;Passed")</f>
-        <v>7</v>
+        <f>COUNTIFS(Items!$L$2:$L$211,"&lt;&gt;",Items!$F$2:$F$211,"&lt;&gt;Passed")</f>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -1496,8 +1496,8 @@
         </is>
       </c>
       <c r="B35" s="0">
-        <f>COUNTIFS(Items!$H$2:$H$196,"&lt;&gt;")</f>
-        <v>55</v>
+        <f>COUNTIFS(Items!$H$2:$H$211,"&lt;&gt;")</f>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The module badge aligns with the first line of the role description; long descriptions wrap below it; the top-right actions stay at the top; cards in one row keep one height with bottom-aligned actions; correct in both themes and at 375, 800, 1280 and 1600 px.</t>
+          <t xml:space="preserve">The module pill, description and actions share one centered line of one height for every card; the description ends in an ellipsis when it does not fit (see R81-10); correct in both themes and at 320, 375, 800, 1280 and 1600 px.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Root cause: a later override centred the badge against the whole multiline description and let the actions wrap below it. Fixed with first-baseline alignment (R8 phase 1).</t>
+          <t xml:space="preserve">Root cause: a later override centred the badge against the whole multiline description and let the actions wrap below it. Fixed with first-baseline alignment (R8 phase 1). Superseded in R8 addendum: the header no longer wraps; the full description is available on demand (R81-10).</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No throttling of failed Basic logins; group-readable secret files are accepted (documented limitations).</t>
+          <t xml:space="preserve">No throttling of failed Basic logins; group-readable secret files are accepted (documented limitations). Update R8.1: failed Basic sign-ins are throttled (R81-01) and group-readable secrets need an explicit opt-in (R81-02).</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Throttle failed logins at the gateway or in the application, and reject group-readable secret files after a compatibility review of systemd and container secret mounts.</t>
+          <t xml:space="preserve">Share throttle state across workers if the runtime ever scales out.</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Throttling and group permissions are open decisions (SECURITY_REVIEW_R8).</t>
+          <t xml:space="preserve">Throttling is per process (see R81-01); distributed guessing relies on the 32 character secret.</t>
         </is>
       </c>
       <c r="P191" s="2" t="inlineStr">
@@ -20535,6 +20535,1461 @@
         </is>
       </c>
       <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-01</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security and Data Integrity</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server › Failed Basic sign-in throttling</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repeated wrong Basic credentials from one client lock that client out with 429 and Retry-After (default 5 failures, 60 s, doubling to 15 min); correct credentials are refused during the lock-out and accepted after it; other clients, health probes and requests without credentials are unaffected; forwarded headers from an untrusted peer change nothing.</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_auth_throttle.py; backend/tests/test_security_surface.py</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1 (SEC-02). Automated tests use a fake clock and a TestClient; no real network, proxy or multi-worker deployment was exercised.</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-02</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Share counters between workers or hosts, or throttle per forwarded identity at the gateway.</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On a test server with Basic authentication, send six wrong passwords from one browser, confirm the 429 page and wait the Retry-After time, then sign in; repeat behind your reverse proxy with SAP_LENS_TRUSTED_PROXIES set and confirm other users are not locked out.</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State is per process and lost on restart; clients behind one NAT or an unlisted proxy share a lock-out; distributed guessing is slowed, not stopped.</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/SECURITY.md; backend/deployment.py; backend/main.py</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-02</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security and Data Integrity</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server › Access secret file permissions (Linux)</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A new secret is created owner-only (0600); an existing secret readable by other users, or writable or executable by its group, is refused; group read (0640) is accepted only with SAP_LENS_AUTH_SECRET_GROUP_READ=1 and a group the service account belongs to; every refusal names the file, its mode and the fix; the file is never changed.</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_secret_file_policy.py; backend/tests/test_security_surface.py</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1 (SEC-03). Judged on the opened file; symlinks resolve to their target.</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-03</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the owner and effective access through the service account, not only the mode.</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On a Linux host start the server with a 0644, a 0640 and a 0600 secret (with and without the opt-in) and read the messages; confirm the systemd service and the Docker compose installation still start.</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An existing 0640 secret needs chmod 600 or the opt-in (migration step, documented). Not exercised under real systemd or Docker here.</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/SECURITY.md; backend/deployment.py; backend/server.py; compose.yml</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-03</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows service › Secret file ACL</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The installed secret file grants access only to SYSTEM, Administrators and read access to the service account; a manually created secret with broader access is noticed by the administrator (the runtime does not verify an ACL).</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_contracts.py</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provisioning applies the ACL with icacls (manage-server-service.ps1). Windows ACLs are not evaluated by the Linux tests and not checked at runtime.</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-03</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the ACL at start (icacls or the Win32 API) and warn like the POSIX check.</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On Windows run icacls on the secret after installation and after any manual replacement; start the service and sign in.</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked on a Windows host: not run in this validation.</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/WINDOWS_SERVICE.md; scripts/manage-server-service.ps1</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partially implemented</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-04</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD Reports</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD › Reports › PDF</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A PDF built from a review period lists risk names and descriptions in the findings section and activity names and descriptions in the appendices, each with its source (Imported, Local fallback or Not available) and a source legend; a file without descriptions produces the report as before.</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_sod_report_metadata.py; backend/tests/test_sod_reports.py</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1. Layout was checked through the model and file validity, not by looking at pages.</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Show transaction descriptions with their source in the same tables.</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generate a PDF for a period captured from a CSV with description columns and read the tables and legend; try a period captured before descriptions were retained.</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A description with characters outside the bundled PDF font fails the PDF with an explicit message (DOCX works).</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/features/SOD.md; backend/sod_reports.py; backend/sod_metadata.py</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-05</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD Reports</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD › Reports › DOCX</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The editable DOCX contains the same description tables, source labels and legend as the PDF, with special characters and long text intact and markup shown as text.</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_sod_report_metadata.py; backend/tests/test_sod_reports.py</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1; content checked in the document XML.</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open the DOCX in Word and read the Source column, the legend and a long description.</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not opened in Word in this validation.</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/features/SOD.md; backend/sod_reports.py</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-06</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD Reports</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD › Reports › Description provenance</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imported text wins, local business text is shown only where the import has none and is labelled Local fallback, a differing local text is reported but never mixed in, and nothing is generated for a missing description.</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_sod_report_metadata.py; backend/tests/test_sod_metadata.py</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The report uses the resolver that also serves the pills and Settings.</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compare one risk and one activity across the pill popover, Settings and the report.</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/sod_metadata.py; docs/data/SOD_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-07</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review Periods</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review Periods › Frozen descriptions</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A period report never shows descriptions imported or edited after the period was captured; an approved period keeps its report model checksum; a period captured before R8.1 shows only its frozen local text and says that imported descriptions were not retained; decisions and approvals are unchanged.</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_sod_report_metadata.py; backend/tests/test_sod_periods_v2.py</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descriptions are stored inside the immutable snapshot (metadata version 1).</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approve a period, import a CSV with different descriptions, regenerate the report and compare; open a period created before the upgrade.</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legacy snapshots cannot show imported descriptions; recapturing a period replaces its copy by design.</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/features/SOD.md; backend/sod_periods.py</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-08</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settings and Data Sources</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD Matrix › Legacy files in reports</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A SoD Matrix CSV without any optional description column, or with partly filled ones, still imports, reviews and reports; missing descriptions never block a PDF or DOCX.</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_sod_report_metadata.py; backend/tests/test_sod_metadata.py</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Old datasets produce the report tables they always did.</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run the report on your existing production-shaped export.</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No real upstream export was available.</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/data/SOD_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-09</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Component Library</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Components › Select dropdown family</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard selects, the searchable select and the multi-select filter open the same list surface (background, border, radius, spacing, hover, accent and check mark for the selected option); long labels wrap, disabled options cannot be chosen, the list stays inside the viewport and above dialogs and side panels, and works with mouse, keyboard, Escape and screen readers, in both themes.</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend/tests/select-family.spec.ts; frontend/tests/a11y-audit.spec.ts</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented as an addendum to R8; the native select element is kept for value, validation and labels.</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open Component Library › Demo select, Demo searchable role and Demo areas in light and dark at 375, 800, 1280 and 1600 px and compare them; try the selects inside the demo dialog and side panel and a screen reader.</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multiple or sized selects keep the browser control; not tried with a screen reader or on a touch device.</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/architecture/COMPONENTS.md; frontend/src/components/Shared/Select.tsx</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-10</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role Lookup</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role Lookup › Card header description</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The module pill, description and actions share one centered line of one height for every card; a description that does not fit ends in an ellipsis and reveals its full text on hover, keyboard focus, click or tap; a description that fits has no control and no tooltip; actions never shrink; correct with long English and French text, at 320 to 1600 px and in both themes.</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend/tests/r8-ui-polish.spec.ts; frontend/tests/a11y-audit.spec.ts</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Addendum to R8-01 (which described the earlier wrapping header). The visible part is short at 375 px by design; the full text is on demand.</t>
+        </is>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resize the browser and zoom to 200 and 400 percent on Role Lookup with long descriptions, in both themes.</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At 375 px or less only a few characters of the description remain visible beside the pill and two actions.</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/architecture/COMPONENTS.md; frontend/src/components/Shared/TruncatedText.tsx</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-11</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository › Ruff and ESLint</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ruff and ESLint run in Fast Validation, Full Validation and the local profiles, fail on errors and on new ESLint warnings beyond the recorded backlog, and a documented command reproduces each.</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_workflows.py; backend/tests/test_test_profiles.py</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correctness rules only; no reformatting.</t>
+        </is>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run python -m ruff check backend scripts and npm run lint in frontend; read the Fast Validation summary on GitHub.</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESLint backlog: 30 hook-dependency warnings and 81 any uses in specs.</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/development/TESTING.md; ruff.toml; frontend/eslint.config.js</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-12</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository › Test process isolation</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Browser test servers remove their temporary directories when stopped, the runner reports busy ports instead of colliding and stops only processes it started.</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_test_profiles.py</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Found 616 leaked directories (1.9 GB) before the fix.</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run a browser spec and check that no sap-lens-browser-* directory and no server process remain.</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/development/TESTING.md; scripts/serve-browser-tests.py; scripts/run-tests.py</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-13</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository › Parallel regression</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The regression runs the browser suite in up to three isolated processes with deterministic distribution, per-process attribution and the same results as a serial run.</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_test_profiles.py</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See R8_1_STABILIZATION.md for the measurements and the one load-dependent failure observed.</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run regression --browser-jobs auto on a 4 CPU host and compare with --browser-jobs 1 when a result is doubtful.</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPU-bound: gains were 1.6x to 1.7x on 4 vCPUs; not measured on CI runners.</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/development/TESTING.md; docs/development/R8_1_STABILIZATION.md</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-14</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desktop and Startup</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows desktop and service › R8.1 changes</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On Windows the desktop application, the server mode with Basic authentication (throttling, secret ACL) and the Windows service start, sign in, lock out and recover as documented, and the select dropdowns, truncated descriptions and report descriptions work in WebView2.</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_contracts.py; backend/tests/test_desktop.py</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Native Windows, WebView2, service control and installer behaviour were not validated.</t>
+        </is>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Install the desktop build and the service on Windows 11 at 100, 150 and 200 percent scaling and walk the R81 items.</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked here: no Windows host.</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/WINDOWS_SERVICE.md; docs/architecture/DESKTOP.md</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partially implemented</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-15</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker and systemd › R8.1 changes</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Docker installation (0640 secret with the explicit opt-in) and the hardened systemd unit (seven added sandbox directives) start, serve and restart on real hosts.</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_contracts.py; backend/tests/test_server.py</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The unit passed systemd-analyze verify; it was not booted. Docker was not run.</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-07</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Install both on a test host, check journalctl or docker logs, sign in, restart.</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked here: no real systemd or Docker runtime.</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/LINUX_DOCKER.md; docs/deployment/LINUX_NATIVE.md; deploy/linux/sap-lens.service</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partially implemented</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not started</t>
         </is>
@@ -21069,12 +22524,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No throttling of failed Basic logins; group-readable secret files are accepted (documented limitations).</t>
+          <t xml:space="preserve">No throttling of failed Basic logins; group-readable secret files are accepted (documented limitations). Update R8.1: failed Basic sign-ins are throttled (R81-01) and group-readable secrets need an explicit opt-in (R81-02).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Throttling and group permissions are open decisions (SECURITY_REVIEW_R8).</t>
+          <t xml:space="preserve">Throttling is per process (see R81-01); distributed guessing relies on the 32 character secret.</t>
         </is>
       </c>
     </row>
@@ -21204,8 +22659,176 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security and Data Integrity</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server › Failed Basic sign-in throttling</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-02</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1 (SEC-02). Automated tests use a fake clock and a TestClient; no real network, proxy or multi-worker deployment was exercised.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State is per process and lost on restart; clients behind one NAT or an unlisted proxy share a lock-out; distributed guessing is slowed, not stopped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-02</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security and Data Integrity</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server › Access secret file permissions (Linux)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-03</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1 (SEC-03). Judged on the opened file; symlinks resolve to their target.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An existing 0640 secret needs chmod 600 or the opt-in (migration step, documented). Not exercised under real systemd or Docker here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-03</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows service › Secret file ACL</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-03</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provisioning applies the ACL with icacls (manage-server-service.ps1). Windows ACLs are not evaluated by the Linux tests and not checked at runtime.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked on a Windows host: not run in this validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-15</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker and systemd › R8.1 changes</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-07</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The unit passed systemd-analyze verify; it was not booted. Docker was not run.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked here: no real systemd or Docker runtime.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H18"/>
   <conditionalFormatting sqref="E2:E2000">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Passed"</formula>
@@ -21488,12 +23111,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Throttle failed logins at the gateway or in the application, and reject group-readable secret files after a compatibility review of systemd and container secret mounts.</t>
+          <t xml:space="preserve">Share throttle state across workers if the runtime ever scales out.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No throttling of failed Basic logins; group-readable secret files are accepted (documented limitations).</t>
+          <t xml:space="preserve">No throttling of failed Basic logins; group-readable secret files are accepted (documented limitations). Update R8.1: failed Basic sign-ins are throttled (R81-01) and group-readable secrets need an explicit opt-in (R81-02).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -21586,8 +23209,176 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security and Data Integrity</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server › Failed Basic sign-in throttling</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Share counters between workers or hosts, or throttle per forwarded identity at the gateway.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1 (SEC-02). Automated tests use a fake clock and a TestClient; no real network, proxy or multi-worker deployment was exercised.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-02</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security and Data Integrity</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server › Access secret file permissions (Linux)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the owner and effective access through the service account, not only the mode.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1 (SEC-03). Judged on the opened file; symlinks resolve to their target.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-03</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows service › Secret file ACL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the ACL at start (icacls or the Win32 API) and warn like the POSIX check.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provisioning applies the ACL with icacls (manage-server-service.ps1). Windows ACLs are not evaluated by the Linux tests and not checked at runtime.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-04</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD Reports</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SoD › Reports › PDF</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Show transaction descriptions with their source in the same tables.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented in R8.1. Layout was checked through the model and file validity, not by looking at pages.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H12"/>
   <conditionalFormatting sqref="E2:E2000">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Passed"</formula>

--- a/docs/validation/validation-tracker.xlsx
+++ b/docs/validation/validation-tracker.xlsx
@@ -133,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ValidationItems" displayName="ValidationItems" ref="A1:S211" totalsRowShown="0">
-  <autoFilter ref="A1:S211"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ValidationItems" displayName="ValidationItems" ref="A1:S212" totalsRowShown="0">
+  <autoFilter ref="A1:S212"/>
   <tableColumns count="19">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -267,39 +267,39 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6)</f>
         <v>9</v>
       </c>
       <c r="C6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,C$5)</f>
         <v>9</v>
       </c>
       <c r="D6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A6,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$G$2:$G$212,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K6" s="4">
@@ -318,39 +318,39 @@
         </is>
       </c>
       <c r="B7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7)</f>
         <v>10</v>
       </c>
       <c r="C7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,C$5)</f>
         <v>10</v>
       </c>
       <c r="D7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A7,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$G$2:$G$212,"Pending")</f>
         <v>10</v>
       </c>
       <c r="K7" s="4">
@@ -369,39 +369,39 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8)</f>
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,C$5)</f>
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,F$5)</f>
         <v>1</v>
       </c>
       <c r="G8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A8,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$G$2:$G$212,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K8" s="4">
@@ -420,39 +420,39 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9)</f>
         <v>9</v>
       </c>
       <c r="C9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,C$5)</f>
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A9,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$G$2:$G$212,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K9" s="4">
@@ -471,39 +471,39 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10)</f>
         <v>9</v>
       </c>
       <c r="C10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,C$5)</f>
         <v>9</v>
       </c>
       <c r="D10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A10,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$G$2:$G$212,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K10" s="4">
@@ -522,39 +522,39 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11)</f>
         <v>5</v>
       </c>
       <c r="C11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,C$5)</f>
         <v>5</v>
       </c>
       <c r="D11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A11,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$G$2:$G$212,"Pending")</f>
         <v>5</v>
       </c>
       <c r="K11" s="4">
@@ -573,39 +573,39 @@
         </is>
       </c>
       <c r="B12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,C$5)</f>
         <v>5</v>
       </c>
       <c r="D12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A12,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$G$2:$G$212,"Pending")</f>
         <v>5</v>
       </c>
       <c r="K12" s="4">
@@ -624,39 +624,39 @@
         </is>
       </c>
       <c r="B13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13)</f>
         <v>9</v>
       </c>
       <c r="C13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,C$5)</f>
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A13,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$G$2:$G$212,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K13" s="4">
@@ -675,39 +675,39 @@
         </is>
       </c>
       <c r="B14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14)</f>
         <v>17</v>
       </c>
       <c r="C14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,C$5)</f>
         <v>17</v>
       </c>
       <c r="D14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A14,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$G$2:$G$212,"Pending")</f>
         <v>17</v>
       </c>
       <c r="K14" s="4">
@@ -726,39 +726,39 @@
         </is>
       </c>
       <c r="B15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,C$5)</f>
         <v>4</v>
       </c>
       <c r="D15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A15,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$G$2:$G$212,"Pending")</f>
         <v>4</v>
       </c>
       <c r="K15" s="4">
@@ -777,39 +777,39 @@
         </is>
       </c>
       <c r="B16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16)</f>
         <v>9</v>
       </c>
       <c r="C16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,C$5)</f>
         <v>9</v>
       </c>
       <c r="D16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A16,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$G$2:$G$212,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K16" s="4">
@@ -828,39 +828,39 @@
         </is>
       </c>
       <c r="B17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17)</f>
         <v>15</v>
       </c>
       <c r="C17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,C$5)</f>
         <v>14</v>
       </c>
       <c r="D17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,F$5)</f>
         <v>1</v>
       </c>
       <c r="G17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A17,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$G$2:$G$212,"Pending")</f>
         <v>15</v>
       </c>
       <c r="K17" s="4">
@@ -879,39 +879,39 @@
         </is>
       </c>
       <c r="B18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18)</f>
         <v>10</v>
       </c>
       <c r="C18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,C$5)</f>
         <v>10</v>
       </c>
       <c r="D18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A18,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$G$2:$G$212,"Pending")</f>
         <v>10</v>
       </c>
       <c r="K18" s="4">
@@ -930,39 +930,39 @@
         </is>
       </c>
       <c r="B19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19)</f>
         <v>7</v>
       </c>
       <c r="C19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,C$5)</f>
         <v>7</v>
       </c>
       <c r="D19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A19,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$G$2:$G$212,"Pending")</f>
         <v>7</v>
       </c>
       <c r="K19" s="4">
@@ -981,39 +981,39 @@
         </is>
       </c>
       <c r="B20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20)</f>
         <v>23</v>
       </c>
       <c r="C20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,C$5)</f>
         <v>23</v>
       </c>
       <c r="D20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A20,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$G$2:$G$212,"Pending")</f>
         <v>23</v>
       </c>
       <c r="K20" s="4">
@@ -1032,39 +1032,39 @@
         </is>
       </c>
       <c r="B21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,C$5)</f>
         <v>2</v>
       </c>
       <c r="D21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A21,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$G$2:$G$212,"Pending")</f>
         <v>2</v>
       </c>
       <c r="K21" s="4">
@@ -1083,39 +1083,39 @@
         </is>
       </c>
       <c r="B22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22)</f>
         <v>6</v>
       </c>
       <c r="C22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,C$5)</f>
         <v>6</v>
       </c>
       <c r="D22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A22,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$G$2:$G$212,"Pending")</f>
         <v>6</v>
       </c>
       <c r="K22" s="4">
@@ -1134,39 +1134,39 @@
         </is>
       </c>
       <c r="B23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23)</f>
         <v>23</v>
       </c>
       <c r="C23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,C$5)</f>
         <v>22</v>
       </c>
       <c r="D23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,F$5)</f>
         <v>1</v>
       </c>
       <c r="G23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A23,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$G$2:$G$212,"Pending")</f>
         <v>23</v>
       </c>
       <c r="K23" s="4">
@@ -1185,39 +1185,39 @@
         </is>
       </c>
       <c r="B24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24)</f>
         <v>4</v>
       </c>
       <c r="C24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,C$5)</f>
         <v>2</v>
       </c>
       <c r="D24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,G$5)</f>
         <v>2</v>
       </c>
       <c r="H24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A24,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$G$2:$G$212,"Pending")</f>
         <v>4</v>
       </c>
       <c r="K24" s="4">
@@ -1236,40 +1236,40 @@
         </is>
       </c>
       <c r="B25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25)</f>
+        <v>9</v>
+      </c>
+      <c r="C25" s="0">
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,C$5)</f>
         <v>8</v>
       </c>
-      <c r="C25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,C$5)</f>
-        <v>7</v>
-      </c>
       <c r="D25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,G$5)</f>
         <v>1</v>
       </c>
       <c r="H25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A25,Items!$G$2:$G$211,"Pending")</f>
-        <v>8</v>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$G$2:$G$212,"Pending")</f>
+        <v>9</v>
       </c>
       <c r="K25" s="4">
         <f>IF(B25-G25=0,0,(D25+E25+F25)/(B25-G25))</f>
@@ -1287,39 +1287,39 @@
         </is>
       </c>
       <c r="B26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26)</f>
         <v>3</v>
       </c>
       <c r="C26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,C$5)</f>
         <v>3</v>
       </c>
       <c r="D26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A26,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$G$2:$G$212,"Pending")</f>
         <v>3</v>
       </c>
       <c r="K26" s="4">
@@ -1338,39 +1338,39 @@
         </is>
       </c>
       <c r="B27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27)</f>
         <v>14</v>
       </c>
       <c r="C27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,C$5)</f>
         <v>14</v>
       </c>
       <c r="D27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,D$5)</f>
         <v>0</v>
       </c>
       <c r="E27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,E$5)</f>
         <v>0</v>
       </c>
       <c r="F27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,F$5)</f>
         <v>0</v>
       </c>
       <c r="G27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,G$5)</f>
         <v>0</v>
       </c>
       <c r="H27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$F$2:$F$211,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,H$5)</f>
         <v>0</v>
       </c>
       <c r="I27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$G$2:$G$211,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$G$2:$G$212,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$211,$A27,Items!$G$2:$G$211,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$G$2:$G$212,"Pending")</f>
         <v>14</v>
       </c>
       <c r="K27" s="4">
@@ -1390,11 +1390,11 @@
       </c>
       <c r="B28" s="5">
         <f>SUM(B6:B27)</f>
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C28" s="5">
         <f>SUM(C6:C27)</f>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D28" s="5">
         <f>SUM(D6:D27)</f>
@@ -1422,11 +1422,11 @@
       </c>
       <c r="J28" s="5">
         <f>SUM(J6:J27)</f>
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K28" s="4">
         <f>IF(B28-G28=0,0,(D28+E28+F28)/(B28-G28))</f>
-        <v>0.014286</v>
+        <v>0.014218</v>
       </c>
       <c r="L28" s="4">
         <f>IF(B28-G28=0,0,H28/(B28-G28))</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="B31" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$211,"Failed")</f>
+        <f>COUNTIFS(Items!$F$2:$F$212,"Failed")</f>
         <v>0</v>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B32" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$211,"Needs improvement")</f>
+        <f>COUNTIFS(Items!$F$2:$F$212,"Needs improvement")</f>
         <v>3</v>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B33" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$211,"Blocked")</f>
+        <f>COUNTIFS(Items!$F$2:$F$212,"Blocked")</f>
         <v>3</v>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B34" s="0">
-        <f>COUNTIFS(Items!$L$2:$L$211,"&lt;&gt;",Items!$F$2:$F$211,"&lt;&gt;Passed")</f>
+        <f>COUNTIFS(Items!$L$2:$L$212,"&lt;&gt;",Items!$F$2:$F$212,"&lt;&gt;Passed")</f>
         <v>11</v>
       </c>
     </row>
@@ -1496,8 +1496,8 @@
         </is>
       </c>
       <c r="B35" s="0">
-        <f>COUNTIFS(Items!$H$2:$H$211,"&lt;&gt;")</f>
-        <v>70</v>
+        <f>COUNTIFS(Items!$H$2:$H$212,"&lt;&gt;")</f>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -21990,6 +21990,103 @@
         </is>
       </c>
       <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R81-16</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Build Deployment Packages › Build selection</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The operating system (all, windows, linux) and package (all or one) inputs build exactly the documented packages; an incompatible pair fails in the first job before validation or any packaging runner starts; unselected packages are skipped and start no runner; the summary lists every package as selected or skipped; publication takes only selected, verified packages and is never blocked or widened by skipped ones.</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_selection.py; backend/tests/test_deployment_release.py; backend/tests/test_workflows.py</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented as an R8.1 follow-up. Verified offline: planner, resolver, workflow job conditions and publication gating; no workflow was dispatched.</t>
+        </is>
+      </c>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After approval, dispatch a build-only run for windows/all, linux/all and one rejected pair (windows with linux-docker) and read the Resolve Build Selection summary; check that skipped jobs start no runner.</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not run on GitHub: the skipped-job and partial-publication behaviour is verified through offline models only.</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/BUILD.md; .github/workflows/build-deployments.yml; scripts/deployment-release.py</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not started</t>
         </is>

--- a/docs/validation/validation-tracker.xlsx
+++ b/docs/validation/validation-tracker.xlsx
@@ -22013,7 +22013,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The operating system (all, windows, linux) and package (all or one) inputs build exactly the documented packages; an incompatible pair fails in the first job before validation or any packaging runner starts; unselected packages are skipped and start no runner; the summary lists every package as selected or skipped; publication takes only selected, verified packages and is never blocked or widened by skipped ones.</t>
+          <t xml:space="preserve">GitHub Actions shows one build_target dropdown (all, windows-all, windows-desktop, windows-service, linux-all, linux-docker, linux-native) and every choice is valid; the selected packages are built independently, unselected packages are skipped and start no runner, the summary shows the target and resolved packages, and publication takes only selected, verified packages and is never blocked or widened by skipped ones.</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implemented as an R8.1 follow-up. Verified offline: planner, resolver, workflow job conditions and publication gating; no workflow was dispatched.</t>
+          <t xml:space="preserve">Implemented as an R8.1 follow-up; a two-input version (operating_system and package) was replaced by the single dropdown because incompatible choices could not be hidden. Verified offline: planner, resolver, workflow job conditions and publication gating; no workflow was dispatched.</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">After approval, dispatch a build-only run for windows/all, linux/all and one rejected pair (windows with linux-docker) and read the Resolve Build Selection summary; check that skipped jobs start no runner.</t>
+          <t xml:space="preserve">After approval, dispatch build-only runs for windows-all, linux-all and one single package and read the Resolve Build Selection summary; check that skipped jobs start no runner and that the dropdown shows exactly seven choices.</t>
         </is>
       </c>
       <c r="O212" s="2" t="inlineStr">

--- a/docs/validation/validation-tracker.xlsx
+++ b/docs/validation/validation-tracker.xlsx
@@ -133,8 +133,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ValidationItems" displayName="ValidationItems" ref="A1:S212" totalsRowShown="0">
-  <autoFilter ref="A1:S212"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ValidationItems" displayName="ValidationItems" ref="A1:S225" totalsRowShown="0">
+  <autoFilter ref="A1:S225"/>
   <tableColumns count="19">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Area"/>
@@ -267,39 +267,39 @@
         </is>
       </c>
       <c r="B6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6)</f>
         <v>9</v>
       </c>
       <c r="C6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$F$2:$F$225,C$5)</f>
         <v>9</v>
       </c>
       <c r="D6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J6" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A6,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A6,Items!$G$2:$G$225,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K6" s="4">
@@ -318,39 +318,39 @@
         </is>
       </c>
       <c r="B7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7)</f>
         <v>10</v>
       </c>
       <c r="C7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$F$2:$F$225,C$5)</f>
         <v>10</v>
       </c>
       <c r="D7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J7" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A7,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A7,Items!$G$2:$G$225,"Pending")</f>
         <v>10</v>
       </c>
       <c r="K7" s="4">
@@ -369,39 +369,39 @@
         </is>
       </c>
       <c r="B8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8)</f>
         <v>9</v>
       </c>
       <c r="C8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$F$2:$F$225,C$5)</f>
         <v>8</v>
       </c>
       <c r="D8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$F$2:$F$225,F$5)</f>
         <v>1</v>
       </c>
       <c r="G8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J8" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A8,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A8,Items!$G$2:$G$225,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K8" s="4">
@@ -420,39 +420,39 @@
         </is>
       </c>
       <c r="B9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9)</f>
         <v>9</v>
       </c>
       <c r="C9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$F$2:$F$225,C$5)</f>
         <v>9</v>
       </c>
       <c r="D9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J9" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A9,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A9,Items!$G$2:$G$225,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K9" s="4">
@@ -471,39 +471,39 @@
         </is>
       </c>
       <c r="B10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10)</f>
         <v>9</v>
       </c>
       <c r="C10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$F$2:$F$225,C$5)</f>
         <v>9</v>
       </c>
       <c r="D10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J10" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A10,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A10,Items!$G$2:$G$225,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K10" s="4">
@@ -522,39 +522,39 @@
         </is>
       </c>
       <c r="B11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11)</f>
         <v>5</v>
       </c>
       <c r="C11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$F$2:$F$225,C$5)</f>
         <v>5</v>
       </c>
       <c r="D11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J11" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A11,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A11,Items!$G$2:$G$225,"Pending")</f>
         <v>5</v>
       </c>
       <c r="K11" s="4">
@@ -573,39 +573,39 @@
         </is>
       </c>
       <c r="B12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12)</f>
         <v>5</v>
       </c>
       <c r="C12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$F$2:$F$225,C$5)</f>
         <v>5</v>
       </c>
       <c r="D12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J12" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A12,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A12,Items!$G$2:$G$225,"Pending")</f>
         <v>5</v>
       </c>
       <c r="K12" s="4">
@@ -624,39 +624,39 @@
         </is>
       </c>
       <c r="B13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13)</f>
         <v>9</v>
       </c>
       <c r="C13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$F$2:$F$225,C$5)</f>
         <v>9</v>
       </c>
       <c r="D13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J13" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A13,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A13,Items!$G$2:$G$225,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K13" s="4">
@@ -675,39 +675,39 @@
         </is>
       </c>
       <c r="B14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14)</f>
         <v>17</v>
       </c>
       <c r="C14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$F$2:$F$225,C$5)</f>
         <v>17</v>
       </c>
       <c r="D14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A14,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A14,Items!$G$2:$G$225,"Pending")</f>
         <v>17</v>
       </c>
       <c r="K14" s="4">
@@ -726,39 +726,39 @@
         </is>
       </c>
       <c r="B15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15)</f>
         <v>4</v>
       </c>
       <c r="C15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$F$2:$F$225,C$5)</f>
         <v>4</v>
       </c>
       <c r="D15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J15" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A15,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A15,Items!$G$2:$G$225,"Pending")</f>
         <v>4</v>
       </c>
       <c r="K15" s="4">
@@ -777,39 +777,39 @@
         </is>
       </c>
       <c r="B16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16)</f>
         <v>9</v>
       </c>
       <c r="C16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$F$2:$F$225,C$5)</f>
         <v>9</v>
       </c>
       <c r="D16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J16" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A16,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A16,Items!$G$2:$G$225,"Pending")</f>
         <v>9</v>
       </c>
       <c r="K16" s="4">
@@ -828,39 +828,39 @@
         </is>
       </c>
       <c r="B17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17)</f>
         <v>15</v>
       </c>
       <c r="C17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$F$2:$F$225,C$5)</f>
         <v>14</v>
       </c>
       <c r="D17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$F$2:$F$225,F$5)</f>
         <v>1</v>
       </c>
       <c r="G17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J17" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A17,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A17,Items!$G$2:$G$225,"Pending")</f>
         <v>15</v>
       </c>
       <c r="K17" s="4">
@@ -879,39 +879,39 @@
         </is>
       </c>
       <c r="B18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18)</f>
         <v>10</v>
       </c>
       <c r="C18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$F$2:$F$225,C$5)</f>
         <v>10</v>
       </c>
       <c r="D18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A18,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A18,Items!$G$2:$G$225,"Pending")</f>
         <v>10</v>
       </c>
       <c r="K18" s="4">
@@ -930,39 +930,39 @@
         </is>
       </c>
       <c r="B19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19)</f>
         <v>7</v>
       </c>
       <c r="C19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$F$2:$F$225,C$5)</f>
         <v>7</v>
       </c>
       <c r="D19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J19" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A19,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A19,Items!$G$2:$G$225,"Pending")</f>
         <v>7</v>
       </c>
       <c r="K19" s="4">
@@ -981,39 +981,39 @@
         </is>
       </c>
       <c r="B20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20)</f>
         <v>23</v>
       </c>
       <c r="C20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$F$2:$F$225,C$5)</f>
         <v>23</v>
       </c>
       <c r="D20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J20" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A20,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A20,Items!$G$2:$G$225,"Pending")</f>
         <v>23</v>
       </c>
       <c r="K20" s="4">
@@ -1032,39 +1032,39 @@
         </is>
       </c>
       <c r="B21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21)</f>
         <v>2</v>
       </c>
       <c r="C21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$F$2:$F$225,C$5)</f>
         <v>2</v>
       </c>
       <c r="D21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J21" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A21,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A21,Items!$G$2:$G$225,"Pending")</f>
         <v>2</v>
       </c>
       <c r="K21" s="4">
@@ -1083,39 +1083,39 @@
         </is>
       </c>
       <c r="B22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22)</f>
         <v>6</v>
       </c>
       <c r="C22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$F$2:$F$225,C$5)</f>
         <v>6</v>
       </c>
       <c r="D22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J22" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A22,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A22,Items!$G$2:$G$225,"Pending")</f>
         <v>6</v>
       </c>
       <c r="K22" s="4">
@@ -1134,39 +1134,39 @@
         </is>
       </c>
       <c r="B23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23)</f>
         <v>23</v>
       </c>
       <c r="C23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$F$2:$F$225,C$5)</f>
         <v>22</v>
       </c>
       <c r="D23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$F$2:$F$225,F$5)</f>
         <v>1</v>
       </c>
       <c r="G23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J23" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A23,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A23,Items!$G$2:$G$225,"Pending")</f>
         <v>23</v>
       </c>
       <c r="K23" s="4">
@@ -1185,39 +1185,39 @@
         </is>
       </c>
       <c r="B24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24)</f>
         <v>4</v>
       </c>
       <c r="C24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$F$2:$F$225,C$5)</f>
         <v>2</v>
       </c>
       <c r="D24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$F$2:$F$225,G$5)</f>
         <v>2</v>
       </c>
       <c r="H24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J24" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A24,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A24,Items!$G$2:$G$225,"Pending")</f>
         <v>4</v>
       </c>
       <c r="K24" s="4">
@@ -1236,40 +1236,40 @@
         </is>
       </c>
       <c r="B25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25)</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25)</f>
+        <v>22</v>
       </c>
       <c r="C25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,C$5)</f>
-        <v>8</v>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$F$2:$F$225,C$5)</f>
+        <v>21</v>
       </c>
       <c r="D25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$F$2:$F$225,G$5)</f>
         <v>1</v>
       </c>
       <c r="H25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J25" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A25,Items!$G$2:$G$212,"Pending")</f>
-        <v>9</v>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A25,Items!$G$2:$G$225,"Pending")</f>
+        <v>22</v>
       </c>
       <c r="K25" s="4">
         <f>IF(B25-G25=0,0,(D25+E25+F25)/(B25-G25))</f>
@@ -1287,39 +1287,39 @@
         </is>
       </c>
       <c r="B26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26)</f>
         <v>3</v>
       </c>
       <c r="C26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$F$2:$F$225,C$5)</f>
         <v>3</v>
       </c>
       <c r="D26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J26" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A26,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A26,Items!$G$2:$G$225,"Pending")</f>
         <v>3</v>
       </c>
       <c r="K26" s="4">
@@ -1338,39 +1338,39 @@
         </is>
       </c>
       <c r="B27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27)</f>
         <v>14</v>
       </c>
       <c r="C27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,C$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$F$2:$F$225,C$5)</f>
         <v>14</v>
       </c>
       <c r="D27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,D$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$F$2:$F$225,D$5)</f>
         <v>0</v>
       </c>
       <c r="E27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,E$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$F$2:$F$225,E$5)</f>
         <v>0</v>
       </c>
       <c r="F27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,F$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$F$2:$F$225,F$5)</f>
         <v>0</v>
       </c>
       <c r="G27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,G$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$F$2:$F$225,G$5)</f>
         <v>0</v>
       </c>
       <c r="H27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$F$2:$F$212,H$5)</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$F$2:$F$225,H$5)</f>
         <v>0</v>
       </c>
       <c r="I27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$G$2:$G$212,"Approved")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$G$2:$G$225,"Approved")</f>
         <v>0</v>
       </c>
       <c r="J27" s="0">
-        <f>COUNTIFS(Items!$B$2:$B$212,$A27,Items!$G$2:$G$212,"Pending")</f>
+        <f>COUNTIFS(Items!$B$2:$B$225,$A27,Items!$G$2:$G$225,"Pending")</f>
         <v>14</v>
       </c>
       <c r="K27" s="4">
@@ -1390,11 +1390,11 @@
       </c>
       <c r="B28" s="5">
         <f>SUM(B6:B27)</f>
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C28" s="5">
         <f>SUM(C6:C27)</f>
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D28" s="5">
         <f>SUM(D6:D27)</f>
@@ -1422,11 +1422,11 @@
       </c>
       <c r="J28" s="5">
         <f>SUM(J6:J27)</f>
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="K28" s="4">
         <f>IF(B28-G28=0,0,(D28+E28+F28)/(B28-G28))</f>
-        <v>0.014218</v>
+        <v>0.013393</v>
       </c>
       <c r="L28" s="4">
         <f>IF(B28-G28=0,0,H28/(B28-G28))</f>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="B31" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$212,"Failed")</f>
+        <f>COUNTIFS(Items!$F$2:$F$225,"Failed")</f>
         <v>0</v>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B32" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$212,"Needs improvement")</f>
+        <f>COUNTIFS(Items!$F$2:$F$225,"Needs improvement")</f>
         <v>3</v>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="B33" s="0">
-        <f>COUNTIFS(Items!$F$2:$F$212,"Blocked")</f>
+        <f>COUNTIFS(Items!$F$2:$F$225,"Blocked")</f>
         <v>3</v>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B34" s="0">
-        <f>COUNTIFS(Items!$L$2:$L$212,"&lt;&gt;",Items!$F$2:$F$212,"&lt;&gt;Passed")</f>
+        <f>COUNTIFS(Items!$L$2:$L$225,"&lt;&gt;",Items!$F$2:$F$225,"&lt;&gt;Passed")</f>
         <v>11</v>
       </c>
     </row>
@@ -1496,8 +1496,8 @@
         </is>
       </c>
       <c r="B35" s="0">
-        <f>COUNTIFS(Items!$H$2:$H$212,"&lt;&gt;")</f>
-        <v>71</v>
+        <f>COUNTIFS(Items!$H$2:$H$225,"&lt;&gt;")</f>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -22087,6 +22087,1267 @@
         </is>
       </c>
       <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-01</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Windows packaging › Upload path confinement</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows package jobs pass test_server: staged uploads are judged on canonical paths, an alias or 8.3 short data directory works, traversal, symlink escape and invalid names are still refused.</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_server.py (UploadPathTests)</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-run a Windows package build on GitHub after approval and confirm test_server passes on the runner.</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed the test fixture, not the application: confinement is unchanged. Reproduced on Linux with an alias directory. Not run on a Windows runner since the fix.</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/BUILD.md; backend/server.py; backend/tests/test_server.py</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-02</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Fast Validation › Change-based selection</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pushes to work/main and PRs to main run cheap checks chosen from the change: documentation-only skips Node, frontend changes add build/lint/smoke, backend or unmapped paths run the whole backend; no complete browser suite per push.</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_test_profiles.py (ChangeSelectionTests); backend/tests/test_workflows.py</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observe a documentation-only push, a frontend push and a pull request.</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backend-only selection ran on GitHub in about 1.5 minutes (run 41335937097). Frontend and PR paths are verified offline only.</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/CI_CD.md; .github/workflows/validate.yml; scripts/test-map.json; scripts/run-tests.py</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-03</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Full Validation › Manual regression</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full Validation runs only by manual dispatch, runs the complete backend and browser suites, uploads reports, and no other workflow or publication step depends on it.</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_workflows.py</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After approval, dispatch once and check both jobs and the uploaded reports.</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The manual form has not run on GitHub.</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/CI_CD.md; .github/workflows/full-validation.yml</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-04</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Build &amp; Release › No regression prerequisite</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build Deployment Packages and the legacy Windows build run only lightweight checks; no complete backend or browser suite, status check, approval input or receipt entry requires a prior Full Regression.</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_workflows.py; backend/tests/test_deployment_packaging.py; backend/tests/test_release_automation.py</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After approval, dispatch a build-only run and confirm shared validation completes in minutes without the suites.</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baseline run 41331855340 spent about 23 of 24.7 minutes in the shared validation suites; they were removed from the release path. Runtime effect (minutes saved) is not measured on GitHub yet.</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/CI_CD.md; .github/workflows/build-deployments.yml; scripts/deployment-package.py</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-05</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Windows Desktop package</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The windows-desktop target builds, passes the native smoke test and distribution round trip, and uploads a verified archive.</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_windows_package.py</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch windows-desktop after approval and check the artifact and the smoke test.</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a Windows runner; failed before the CICD-01 fix and has not been rerun.</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/WINDOWS_DESKTOP.md; docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-06</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Windows Service package</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The windows-service target builds, verifies the WinSW/SCM package contents and round trip, and uploads a verified archive.</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch windows-service after approval; install on a test host to confirm SCM behavior.</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a Windows runner and a real SCM host; not run.</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/WINDOWS_SERVICE.md; docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-07</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Linux Docker package</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The linux-docker target builds the image archive, passes the container smoke test and round trip.</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_deployment_contracts.py</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch linux-docker after approval; run the image on a test host.</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker was not run locally; no GitHub run since the change.</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/LINUX_DOCKER.md; docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-08</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Linux Native package</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The linux-native target builds the archive, validates the systemd unit and round trip.</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_deployment_contracts.py</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch linux-native after approval; install on a host with systemd.</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Real systemd was not booted; no GitHub run since the change.</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/LINUX_NATIVE.md; docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-09</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Release channels and versions</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alpha, Beta, Release Candidate and Stable produce the expected versions and tags; invalid versions or sequences are rejected; Stable is published only from main; duplicate versions are refused.</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_release.py</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After approval, publish one Beta test release and check tag, flags and assets.</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stable-from-main is enforced in code (plan job and publish). No test release has been published; publication is verified against a fake API only.</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/RELEASES.md; docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-10</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Artifact verification and provenance</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only same-run, same-commit artifacts of selected packages are collected; digests and checksums are verified; a missing, corrupted or unselected artifact stops publication before any release exists.</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critical</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_deployment_release.py; backend/tests/test_deployment_packaging.py</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review a real run: artifact IDs, digests and the sealed receipt.</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offline only; no real publication run.</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/CI_CD.md; docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-11</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › Workflow execution contracts</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The offline contract (triggers, permissions, graph, conditions, policy) fails on any drift, and actionlint passes.</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_workflows.py; backend/tests/test_deployment_selection.py</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run python scripts/check-workflows.py after editing any workflow.</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contracts and actionlint passed on GitHub in run 41335937097. Contracts check structure, not runner behavior.</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scripts/check-workflows.py; docs/deployment/CI_CD.md</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-12</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › CI/CD security</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions are SHA-pinned, checkout does not persist credentials, no pull_request_target, least-privilege tokens, inputs only via env, publication gated by channel environments.</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/tests/test_workflows.py; backend/tests/test_deployment_release.py</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm environment protection rules (required reviewers, main-only for sap-lens-stable) in repository settings.</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository audit: no confirmed issue left open; Stable-from-main gap fixed. Hardening recommendations are listed in the guide. Repository and environment settings cannot be read from the repository.</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/deployment/CI_CD.md; docs/deployment/RELEASES.md</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CICD-13</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server and Deployment</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions › GitHub runtime validation</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each workflow scenario in the matrix is verified by a completed GitHub run recorded with its URL.</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not tested</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After approval, run the smallest set listed in the matrix: Windows package, Linux package, build-only, skipped jobs, safe publication.</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fast Validation backend-only path verified (run 41335937097); the rest is pending. No workflow has been dispatched and no test release published without approval.</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/validation/WORKFLOW_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partially implemented</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unclassified</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not started</t>
         </is>

--- a/docs/validation/validation-tracker.xlsx
+++ b/docs/validation/validation-tracker.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B35" s="0">
         <f>COUNTIFS(Items!$H$2:$H$225,"&lt;&gt;")</f>
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -22518,7 +22518,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_windows_package.py</t>
+          <t xml:space="preserve">backend/tests/test_windows_package.py; backend/tests/test_deployment_packaging.py</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 41340859408 (2026-11-01): Desktop failed during build identity verification: the job omitted SAP_LENS_EXPECTED_BUILD_JSON. Fixed in 6f64b68 by passing shared resolved metadata; targeted CLI/contract checks passed.</t>
         </is>
       </c>
       <c r="L217" s="2" t="inlineStr">
@@ -22553,12 +22553,12 @@
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Needs a Windows runner; failed before the CICD-01 fix and has not been rerun.</t>
+          <t xml:space="preserve">Native Windows package/EXE/WebView2 retest pending; no corrected GitHub run.</t>
         </is>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/deployment/WINDOWS_DESKTOP.md; docs/validation/WORKFLOW_MATRIX.md</t>
+          <t xml:space="preserve">docs/deployment/WINDOWS_DESKTOP.md; docs/validation/WORKFLOW_MATRIX.md; fix: 6f64b68; docs/validation/WORKFLOW_MATRIX.md</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 41340859408 (2026-11-01): Service failed because PyInstaller resolved relative assets under the nested spec directory. Fixed in 6f64b68 with root-absolute inputs; rooted-input contract plus local PyInstaller resolver probe and PowerShell parsing passed.</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -22650,12 +22650,12 @@
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Needs a Windows runner and a real SCM host; not run.</t>
+          <t xml:space="preserve">Windows build and SCM install/start/health/stop/uninstall still require corrected Windows job.</t>
         </is>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/deployment/WINDOWS_SERVICE.md; docs/validation/WORKFLOW_MATRIX.md</t>
+          <t xml:space="preserve">docs/deployment/WINDOWS_SERVICE.md; docs/validation/WORKFLOW_MATRIX.md; fix: 6f64b68; docs/validation/WORKFLOW_MATRIX.md</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -22712,7 +22712,7 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_deployment_contracts.py</t>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 41340859408 (2026-11-01): Linux Docker packaging and verification succeeded in GitHub run 41340859408 at 513d388. Docker code unchanged by the targeted repair.</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -22747,12 +22747,12 @@
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docker was not run locally; no GitHub run since the change.</t>
+          <t xml:space="preserve">No new Docker job dispatched; this does not establish all target-platform acceptance.</t>
         </is>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/deployment/LINUX_DOCKER.md; docs/validation/WORKFLOW_MATRIX.md</t>
+          <t xml:space="preserve">docs/deployment/LINUX_DOCKER.md; docs/validation/WORKFLOW_MATRIX.md; fix: 6f64b68; docs/validation/WORKFLOW_MATRIX.md</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_deployment_contracts.py</t>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; scripts/test-native-deployment.py</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
@@ -22824,7 +22824,7 @@
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 41340859408 (2026-11-01): Native failed before vulnerability analysis: pip_audit module absent. Fixed in 6f64b68 by provisioning existing pinned audit tooling. Canonical archive, runtime audit and user-mode lifecycle passed locally.</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -22844,12 +22844,12 @@
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real systemd was not booted; no GitHub run since the change.</t>
+          <t xml:space="preserve">Corrected GitHub native job and real systemd acceptance pending. Wheel hashes and audit failures remain enforced.</t>
         </is>
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/deployment/LINUX_NATIVE.md; docs/validation/WORKFLOW_MATRIX.md</t>
+          <t xml:space="preserve">docs/deployment/LINUX_NATIVE.md; docs/validation/WORKFLOW_MATRIX.md; fix: 6f64b68; docs/validation/WORKFLOW_MATRIX.md</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">backend/tests/test_deployment_release.py; backend/tests/test_deployment_packaging.py</t>
+          <t xml:space="preserve">backend/tests/test_deployment_packaging.py; backend/tests/test_artifact_zip.py</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 41340859408 (2026-11-01): Run 41340859408 native download matched expected SHA-256. digest-mismatch: error was configuration, not a detected mismatch. Integrity/receipt/provenance tests passed; controls unchanged.</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
@@ -23038,12 +23038,12 @@
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Offline only; no real publication run.</t>
+          <t xml:space="preserve">Repaired Windows/native distribution round trips await actual GitHub jobs.</t>
         </is>
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/deployment/CI_CD.md; docs/validation/WORKFLOW_MATRIX.md</t>
+          <t xml:space="preserve">docs/deployment/CI_CD.md; docs/validation/WORKFLOW_MATRIX.md; fix: 6f64b68; docs/validation/WORKFLOW_MATRIX.md</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">backend/tests/test_workflows.py; backend/tests/test_deployment_packaging.py</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
@@ -23309,7 +23309,7 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 41340859408 (2026-11-01): Run 41340859408: selection, shared validation and Docker passed; Desktop, Service and Native failed before repairs; publish skipped. Repairs locally verified, no new workflow dispatched.</t>
         </is>
       </c>
       <c r="L225" s="2" t="inlineStr">
@@ -23329,12 +23329,12 @@
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fast Validation backend-only path verified (run 41335937097); the rest is pending. No workflow has been dispatched and no test release published without approval.</t>
+          <t xml:space="preserve">Minimum remaining dispatches after approval: linux-native and windows-all build-only on repaired work. Full Regression is not a prerequisite.</t>
         </is>
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/validation/WORKFLOW_MATRIX.md</t>
+          <t xml:space="preserve">docs/validation/WORKFLOW_MATRIX.md; fix: 6f64b68; docs/validation/WORKFLOW_MATRIX.md</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
